--- a/References/TercihAnalizi Database Tables/universities.xlsx
+++ b/References/TercihAnalizi Database Tables/universities.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="689">
   <si>
     <t>id</t>
   </si>
@@ -1791,7 +1791,7 @@
     <t>DOĞU AKDENİZ ÜNİVERSİTESİ (KKTC-GAZİMAĞUSA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3002</t>
@@ -1800,7 +1800,7 @@
     <t>GİRNE AMERİKAN ÜNİVERSİTESİ (KKTC-GİRNE)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3003</t>
@@ -1809,7 +1809,7 @@
     <t>LEFKE AVRUPA ÜNİVERSİTESİ (KKTC-LEFKE)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3004</t>
@@ -1818,7 +1818,7 @@
     <t>ULUSLARARASI KIBRIS ÜNİVERSİTESİ (KKTC-LEFKOŞA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3005</t>
@@ -1827,7 +1827,7 @@
     <t>YAKIN DOĞU ÜNİVERSİTESİ (KKTC-LEFKOŞA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3006</t>
@@ -1836,7 +1836,7 @@
     <t>AKDENİZ KARPAZ ÜNİVERSİTESİ (KKTC-LEFKOŞA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3007</t>
@@ -1845,16 +1845,7 @@
     <t>GİRNE ÜNİVERSİTESİ (KKTC-GİRNE)</t>
   </si>
   <si>
-    <t>foundation</t>
-  </si>
-  <si>
-    <t>3008</t>
-  </si>
-  <si>
-    <t>KIBRIS İLİM ÜNİVERSİTESİ (KKTC-GİRNE)</t>
-  </si>
-  <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3009</t>
@@ -1863,7 +1854,7 @@
     <t>KIBRIS AMERİKAN ÜNİVERSİTESİ (KKTC-LEFKOŞA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3012</t>
@@ -1872,7 +1863,7 @@
     <t>KIBRIS SAĞLIK VE TOPLUM BİLİMLERİ ÜNİVERSİTESİ (KKTC-GÜZELYURT)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3013</t>
@@ -1881,7 +1872,7 @@
     <t>ULUSLARARASI FİNAL ÜNİVERSİTESİ (KKTC-GİRNE)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>4011</t>
@@ -1890,7 +1881,7 @@
     <t>AZERBAYCAN DEVLET PEDAGOJİ ÜNİVERSİTESİ (BAKÜ-AZERBAYCAN)</t>
   </si>
   <si>
-    <t>state</t>
+    <t>international</t>
   </si>
   <si>
     <t>4039</t>
@@ -1899,7 +1890,7 @@
     <t>HOCA AHMET YESEVİ ULUSLARARASI TÜRK-KAZAK ÜNİVERSİTESİ (TÜRKİSTAN-KAZAKİSTAN)*</t>
   </si>
   <si>
-    <t>state</t>
+    <t>international</t>
   </si>
   <si>
     <t>4052</t>
@@ -1908,7 +1899,7 @@
     <t>KIRGIZİSTAN-TÜRKİYE MANAS ÜNİVERSİTESİ (BİŞKEK-KIRGIZİSTAN)*</t>
   </si>
   <si>
-    <t>state</t>
+    <t>international</t>
   </si>
   <si>
     <t>4088</t>
@@ -1917,7 +1908,7 @@
     <t>ULUSLARARASI SARAYBOSNA ÜNİVERSİTESİ (SARAYBOSNA - BOSNA - HERSEK)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>4096</t>
@@ -1926,7 +1917,7 @@
     <t>ULUSLARARASI BALKAN ÜNİVERSİTESİ (ÜSKÜP-MAKEDONYA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>1109</t>
@@ -2034,7 +2025,7 @@
     <t>ADA KENT ÜNİVERSİTESİ (KKTC-GAZİMAĞUSA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3016</t>
@@ -2043,7 +2034,7 @@
     <t>ARKIN YARATICI SANATLAR VE TASARIM ÜNİVERSİTESİ (KKTC-GİRNE)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3017</t>
@@ -2052,7 +2043,7 @@
     <t>BAHÇEŞEHİR KIBRIS ÜNİVERSİTESİ (KKTC-LEFKOŞA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3015</t>
@@ -2061,7 +2052,7 @@
     <t>KIBRIS BATI ÜNİVERSİTESİ (KKTC-GAZİMAĞUSA)</t>
   </si>
   <si>
-    <t>foundation</t>
+    <t>international</t>
   </si>
   <si>
     <t>3018</t>
@@ -2070,34 +2061,25 @@
     <t>RAUF DENKTAŞ ÜNİVERSİTESİ (KKTC-LEFKOŞA)</t>
   </si>
   <si>
-    <t>foundation</t>
-  </si>
-  <si>
-    <t>4013</t>
-  </si>
-  <si>
-    <t>AZERBAYCAN DİLLER ÜNİVERSİTESİ</t>
-  </si>
-  <si>
-    <t>state</t>
-  </si>
-  <si>
-    <t>4017</t>
-  </si>
-  <si>
-    <t>AZERBAYCAN TIP ÜNİVERSİTESİ</t>
-  </si>
-  <si>
-    <t>state</t>
-  </si>
-  <si>
-    <t>4020</t>
-  </si>
-  <si>
-    <t>BAKÜ DEVLET ÜNİVERSİTESİ</t>
-  </si>
-  <si>
-    <t>state</t>
+    <t>international</t>
+  </si>
+  <si>
+    <t>3020</t>
+  </si>
+  <si>
+    <t>KIBRIS AYDIN ÜNİVERSİTESİ (KKTC-GİRNE)</t>
+  </si>
+  <si>
+    <t>international</t>
+  </si>
+  <si>
+    <t>4099</t>
+  </si>
+  <si>
+    <t>TİRAN NEW YORK ÜNİVERSİTESİ (TİRAN-ARNAVUTLUK)</t>
+  </si>
+  <si>
+    <t>international</t>
   </si>
 </sst>
 </file>
@@ -2121,7 +2103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2130,13 +2112,15 @@
       <diagonal/>
     </border>
     <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2146,7 +2130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H228"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6651,7 +6635,7 @@
         <v>592</v>
       </c>
       <c r="H196" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="197">
@@ -6671,7 +6655,7 @@
         <v>595</v>
       </c>
       <c r="H197" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="198">
@@ -6691,7 +6675,7 @@
         <v>598</v>
       </c>
       <c r="H198" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="199">
@@ -6711,7 +6695,7 @@
         <v>601</v>
       </c>
       <c r="H199" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="200">
@@ -6731,7 +6715,7 @@
         <v>604</v>
       </c>
       <c r="H200" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="201">
@@ -6751,7 +6735,7 @@
         <v>607</v>
       </c>
       <c r="H201" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="202">
@@ -6771,12 +6755,12 @@
         <v>610</v>
       </c>
       <c r="H202" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B203">
         <v>220</v>
@@ -6791,12 +6775,12 @@
         <v>613</v>
       </c>
       <c r="H203" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B204">
         <v>220</v>
@@ -6811,12 +6795,12 @@
         <v>616</v>
       </c>
       <c r="H204" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B205">
         <v>220</v>
@@ -6831,12 +6815,12 @@
         <v>619</v>
       </c>
       <c r="H205" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B206">
         <v>220</v>
@@ -6851,12 +6835,12 @@
         <v>622</v>
       </c>
       <c r="H206" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="B207">
         <v>220</v>
@@ -6871,12 +6855,12 @@
         <v>625</v>
       </c>
       <c r="H207" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B208">
         <v>220</v>
@@ -6891,12 +6875,12 @@
         <v>628</v>
       </c>
       <c r="H208" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="B209">
         <v>220</v>
@@ -6911,12 +6895,12 @@
         <v>631</v>
       </c>
       <c r="H209" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B210">
         <v>220</v>
@@ -6931,15 +6915,18 @@
         <v>634</v>
       </c>
       <c r="H210" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B211">
         <v>220</v>
+      </c>
+      <c r="C211">
+        <v>7</v>
       </c>
       <c r="D211" t="s">
         <v>635</v>
@@ -6951,12 +6938,12 @@
         <v>637</v>
       </c>
       <c r="H211" s="1">
-        <v>45721.480115740742</v>
+        <v>45721.528969907406</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B212">
         <v>220</v>
@@ -6979,13 +6966,13 @@
     </row>
     <row r="213">
       <c r="A213">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B213">
         <v>220</v>
       </c>
       <c r="C213">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D213" t="s">
         <v>641</v>
@@ -7002,13 +6989,13 @@
     </row>
     <row r="214">
       <c r="A214">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B214">
         <v>220</v>
       </c>
       <c r="C214">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D214" t="s">
         <v>644</v>
@@ -7025,13 +7012,13 @@
     </row>
     <row r="215">
       <c r="A215">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B215">
         <v>220</v>
       </c>
       <c r="C215">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D215" t="s">
         <v>647</v>
@@ -7048,13 +7035,13 @@
     </row>
     <row r="216">
       <c r="A216">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B216">
         <v>220</v>
       </c>
       <c r="C216">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D216" t="s">
         <v>650</v>
@@ -7071,7 +7058,7 @@
     </row>
     <row r="217">
       <c r="A217">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B217">
         <v>220</v>
@@ -7094,13 +7081,13 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B218">
         <v>220</v>
       </c>
       <c r="C218">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D218" t="s">
         <v>656</v>
@@ -7117,13 +7104,13 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B219">
         <v>220</v>
       </c>
       <c r="C219">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D219" t="s">
         <v>659</v>
@@ -7140,13 +7127,13 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B220">
         <v>220</v>
       </c>
       <c r="C220">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D220" t="s">
         <v>662</v>
@@ -7163,13 +7150,13 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B221">
         <v>220</v>
       </c>
       <c r="C221">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D221" t="s">
         <v>665</v>
@@ -7186,13 +7173,10 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B222">
         <v>220</v>
-      </c>
-      <c r="C222">
-        <v>53</v>
       </c>
       <c r="D222" t="s">
         <v>668</v>
@@ -7204,12 +7188,12 @@
         <v>670</v>
       </c>
       <c r="H222" s="1">
-        <v>45721.528969907406</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B223">
         <v>220</v>
@@ -7224,12 +7208,12 @@
         <v>673</v>
       </c>
       <c r="H223" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B224">
         <v>220</v>
@@ -7244,12 +7228,12 @@
         <v>676</v>
       </c>
       <c r="H224" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B225">
         <v>220</v>
@@ -7264,12 +7248,12 @@
         <v>679</v>
       </c>
       <c r="H225" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B226">
         <v>220</v>
@@ -7284,12 +7268,12 @@
         <v>682</v>
       </c>
       <c r="H226" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B227">
         <v>220</v>
@@ -7303,16 +7287,19 @@
       <c r="F227" t="s">
         <v>685</v>
       </c>
+      <c r="G227" s="2">
+        <v>46107.670543981476</v>
+      </c>
       <c r="H227" s="1">
-        <v>45721.480115740742</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B228">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D228" t="s">
         <v>686</v>
@@ -7323,48 +7310,11 @@
       <c r="F228" t="s">
         <v>688</v>
       </c>
+      <c r="G228" s="2">
+        <v>46107.670543981476</v>
+      </c>
       <c r="H228" s="1">
-        <v>45726.554976851847</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229">
-        <v>353</v>
-      </c>
-      <c r="B229">
-        <v>222</v>
-      </c>
-      <c r="D229" t="s">
-        <v>689</v>
-      </c>
-      <c r="E229" t="s">
-        <v>690</v>
-      </c>
-      <c r="F229" t="s">
-        <v>691</v>
-      </c>
-      <c r="H229" s="1">
-        <v>45726.554976851847</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230">
-        <v>354</v>
-      </c>
-      <c r="B230">
-        <v>223</v>
-      </c>
-      <c r="D230" t="s">
-        <v>692</v>
-      </c>
-      <c r="E230" t="s">
-        <v>693</v>
-      </c>
-      <c r="F230" t="s">
-        <v>694</v>
-      </c>
-      <c r="H230" s="1">
-        <v>45726.554976851847</v>
+        <v>46107.670543981476</v>
       </c>
     </row>
   </sheetData>
